--- a/data/trans_orig/IP05A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>66032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>52951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66902</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>109137</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>130143</t>
+          <t>129100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>21927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59212</t>
+          <t>60967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>12787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311325</t>
+          <t>309315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342554</t>
+          <t>340704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339946</t>
+          <t>340306</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>372819</t>
+          <t>373039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661418</t>
+          <t>662217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>706784</t>
+          <t>704440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97689</t>
+          <t>99711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128995</t>
+          <t>131314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107876</t>
+          <t>108052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139713</t>
+          <t>139720</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214426</t>
+          <t>216033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>259676</t>
+          <t>259075</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>33357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104616</t>
+          <t>105904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>124885</t>
+          <t>125329</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113141</t>
+          <t>113646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>132994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225383</t>
+          <t>225418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>252668</t>
+          <t>253838</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34907</t>
+          <t>34464</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>53460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32362</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51523</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>72043</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98860</t>
+          <t>98960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2172</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>481977</t>
+          <t>480324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>522132</t>
+          <t>519340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520279</t>
+          <t>521328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>563102</t>
+          <t>560492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1015006</t>
+          <t>1013391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1072312</t>
+          <t>1070198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>165609</t>
+          <t>167126</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>203476</t>
+          <t>205417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165286</t>
+          <t>168092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205032</t>
+          <t>204504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345028</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400266</t>
+          <t>399310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30008</t>
+          <t>29855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34583</t>
+          <t>34823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46332</t>
+          <t>46139</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>42777</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55026</t>
+          <t>55004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81867</t>
+          <t>81231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>98901</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18999</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>21704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>38531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8724</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339050</t>
+          <t>338534</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368887</t>
+          <t>370193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352137</t>
+          <t>352956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>381791</t>
+          <t>384145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702237</t>
+          <t>701802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745509</t>
+          <t>745522</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83172</t>
+          <t>82464</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111678</t>
+          <t>112003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88124</t>
+          <t>87342</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116780</t>
+          <t>116066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>178491</t>
+          <t>177341</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>218402</t>
+          <t>217974</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25028</t>
+          <t>24654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>27180</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47123</t>
+          <t>47739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124083</t>
+          <t>123075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>141032</t>
+          <t>141161</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138108</t>
+          <t>137834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>156294</t>
+          <t>155627</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>267376</t>
+          <t>267442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>292867</t>
+          <t>292658</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27654</t>
+          <t>27110</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44257</t>
+          <t>43872</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24717</t>
+          <t>25706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56725</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80521</t>
+          <t>80980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>509154</t>
+          <t>510973</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>544977</t>
+          <t>547347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>547125</t>
+          <t>545335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>583776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1067061</t>
+          <t>1067112</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1119577</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131602</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>164966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>166622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>272046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322383</t>
+          <t>322596</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>48358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35151</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49557</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75933</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95257</t>
+          <t>94638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,11%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17277</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19175</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>12288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30450</t>
+          <t>32155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18236</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277701</t>
+          <t>287536</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381409</t>
+          <t>383471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419738</t>
+          <t>419898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452570</t>
+          <t>450406</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704813</t>
+          <t>704547</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822904</t>
+          <t>822446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44825</t>
+          <t>44617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72516</t>
+          <t>71538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39921</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67600</t>
+          <t>66100</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>93542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>131367</t>
+          <t>130271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138215</t>
+          <t>127060</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>18134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>36294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181496</t>
+          <t>190413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124676</t>
+          <t>124396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>137915</t>
+          <t>138722</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143149</t>
+          <t>143997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164010</t>
+          <t>164897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273904</t>
+          <t>273768</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>299184</t>
+          <t>299223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24375</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8859</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>11967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>457389</t>
+          <t>454155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>559959</t>
+          <t>560814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>614706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>654875</t>
+          <t>656060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1078915</t>
+          <t>1095391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1199255</t>
+          <t>1200342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141307</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>188818</t>
+          <t>191392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135692</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192037</t>
+          <t>182731</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60453</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53282</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66864</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>78,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>58558</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51433</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>66032</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51978</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66828</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60453</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52951</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66273</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>70,95%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129100</t>
+          <t>128396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21544</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15507</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28572</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>28762</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21927</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36447</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21504</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35811</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21544</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15526</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28793</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,28%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -953,67 +953,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7536</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>3,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>3606</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7992</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7636</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,97%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90926</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90926</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90926</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>85208</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>85208</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>85208</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>357694</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>342498</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>374216</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>326780</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>309315</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>340704</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>310161</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>342010</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>357694</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>340306</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>373039</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>662217</t>
+          <t>663631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704440</t>
+          <t>708085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122575</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>106085</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>136269</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>27,6%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>113281</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>99711</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>131314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>98614</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>130431</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>25,15%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>29,15%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>122575</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108052</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>139720</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>24,83%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>216033</t>
+          <t>212123</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>259075</t>
+          <t>257217</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13457</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8795</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10415</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5697</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16728</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16879</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13457</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8053</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19727</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33357</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>493726</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>493726</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>493726</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>653</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>450476</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>450476</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>450476</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>493726</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>493726</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>493726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123801</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>115100</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132487</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>72,56%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>67,46%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>77,65%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>115599</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>105904</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>125329</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>104953</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>124383</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>69,86%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>64,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>75,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123801</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>113646</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132994</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>72,56%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225418</t>
+          <t>223913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>253838</t>
+          <t>252759</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41821</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33347</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>50754</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43753</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34464</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>53460</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35413</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54366</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>41821</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32618</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>51548</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98960</t>
+          <t>100549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2049</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>6114</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2882</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11408</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10986</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2172</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9490</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170610</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170610</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170610</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165465</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165465</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165465</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170610</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170610</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170610</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>541946</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>522212</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>561344</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>500936</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>480324</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>519340</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>480038</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>519877</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>70,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>67,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>73,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>541946</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>521328</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>560492</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>72,3%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1013391</t>
+          <t>1013960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1070198</t>
+          <t>1070692</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -2208,67 +2208,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>185940</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>166706</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>205281</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>24,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>185795</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>167126</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>205417</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>167764</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>206091</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,28%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>185940</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>168092</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>204504</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345489</t>
+          <t>343948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>399310</t>
+          <t>398445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>21657</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15186</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20134</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13796</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28671</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13684</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>28845</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>21657</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>15286</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>29855</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>32676</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>749543</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>749543</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>749543</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>706866</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>749543</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>749543</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>749543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2609,7 +2609,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2777,72 +2777,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>49617</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>43471</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>54736</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>73,82%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>40804</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34823</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46139</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33968</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>46188</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>69,38%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>49617</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>42777</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>55004</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>73,82%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81231</t>
+          <t>81563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>98901</t>
+          <t>98500</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,16%</t>
         </is>
       </c>
     </row>
@@ -2890,72 +2890,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13200</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8124</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18668</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>16099</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11118</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22143</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10618</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22540</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>27,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>13200</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19367</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>22047</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>37877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -3003,72 +3003,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8187</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1911</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5127</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4894</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4393</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8510</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10999</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -3116,57 +3116,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>67210</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>67210</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>67210</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>58814</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>67210</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>67210</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>67210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3233,72 +3233,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>368516</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>352120</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>384911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>354952</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>338534</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>370193</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>339362</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>369993</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>75,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>368516</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>352956</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>384145</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>701802</t>
+          <t>702031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745522</t>
+          <t>745377</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -3346,72 +3346,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101850</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87217</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>118798</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,9%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>96420</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>82464</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>112003</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>82518</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>111302</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>20,49%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>17,53%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101850</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87342</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>116066</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>20,9%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>177341</t>
+          <t>177320</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>217974</t>
+          <t>217212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -3459,72 +3459,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>16871</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10881</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23759</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19178</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13679</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27821</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13497</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26560</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>16871</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10875</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24654</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47739</t>
+          <t>46392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -3572,57 +3572,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>487237</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>487237</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>487237</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>470550</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>470550</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>470550</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>487237</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>487237</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>487237</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3689,72 +3689,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>147512</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138080</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156618</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>78,96%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>73,91%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>83,83%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>133201</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>123075</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>141161</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>123352</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>141630</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>77,69%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,78%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>147512</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>137834</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>155627</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>78,96%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>267442</t>
+          <t>267867</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>292658</t>
+          <t>292429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -3802,72 +3802,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32727</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24127</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41111</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27110</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>43872</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27453</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>45463</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>20,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32727</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25706</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>41714</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56873</t>
+          <t>57156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>81044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -3915,72 +3915,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6590</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12777</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2900</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7111</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6590</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3239</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>12026</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4028,57 +4028,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>186829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>186829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>186829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171457</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171457</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171457</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>186829</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>186829</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>186829</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>565645</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>547488</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>586956</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>528958</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>510973</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>547347</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>509882</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>546778</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>565645</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>545335</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1067112</t>
+          <t>1067524</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1120447</t>
+          <t>1121108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -4258,72 +4258,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>147777</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>128331</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>165703</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>147875</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>130626</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>164966</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>130359</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>166493</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>147777</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>130996</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>166622</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272046</t>
+          <t>271058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322596</t>
+          <t>322005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -4371,72 +4371,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27854</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20078</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23989</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16855</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32600</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17168</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>32524</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>27854</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>19343</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>37074</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -4484,57 +4484,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>700822</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4664,7 +4664,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4832,72 +4832,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39541</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32628</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>45033</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42942</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32983</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48358</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,32%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>88,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35283</t>
+          <t>31376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>85737</t>
+          <t>76615</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74098</t>
+          <t>67889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94638</t>
+          <t>83926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -4945,72 +4945,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10486</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5590</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16835</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7799</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18531</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11968</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19009</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12288</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32155</t>
+          <t>24071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12205</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,51%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3937</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8578</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11177</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -5171,57 +5171,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5288,72 +5288,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>399095</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>384578</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>411636</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,12%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>529</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>356309</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>287536</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>383471</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436312</t>
+          <t>352093</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>419898</t>
+          <t>336353</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>450406</t>
+          <t>365434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>792621</t>
+          <t>751187</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704547</t>
+          <t>729810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822446</t>
+          <t>771012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -5401,72 +5401,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49585</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38516</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>62610</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13,21%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58189</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44617</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>71538</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,53%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52541</t>
+          <t>58888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66100</t>
+          <t>74132</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>110729</t>
+          <t>108473</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93542</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130271</t>
+          <t>126266</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -5514,72 +5514,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25396</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18287</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35532</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46012</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17907</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>127060</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,59%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18134</t>
+          <t>13999</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36294</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72075</t>
+          <t>46863</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190413</t>
+          <t>61247</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -5627,57 +5627,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>474076</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>474076</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>474076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514916</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514916</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514916</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>975425</t>
+          <t>906523</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975425</t>
+          <t>906523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>975425</t>
+          <t>906523</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132242</t>
+          <t>145466</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124396</t>
+          <t>135952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138722</t>
+          <t>152725</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>155888</t>
+          <t>133186</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143997</t>
+          <t>125118</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164897</t>
+          <t>139366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>288131</t>
+          <t>278652</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273768</t>
+          <t>267904</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>299223</t>
+          <t>287670</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -5857,72 +5857,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16506</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10784</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24646</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12883</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7482</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20112</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>12440</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33677</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>21008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -5970,72 +5970,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5490</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11773</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9093</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11967</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6083,57 +6083,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6200,72 +6200,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>584101</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>565795</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>601647</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>81,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>531493</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>454155</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>560814</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>634995</t>
+          <t>522354</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>614706</t>
+          <t>506155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>656060</t>
+          <t>537882</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1166488</t>
+          <t>1106454</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1095391</t>
+          <t>1082258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1200342</t>
+          <t>1129283</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -6313,72 +6313,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>76577</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>62287</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93238</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>78871</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>64263</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>96166</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>76502</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67849</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103397</t>
+          <t>90246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>164174</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141994</t>
+          <t>133996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>191392</t>
+          <t>177105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -6426,72 +6426,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>37591</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>49619</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>54374</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>25639</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>139205</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>93401</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>53384</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182731</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -6539,57 +6539,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
